--- a/SGC-CKN/Excel/bf6734bd-047d-4687-8d8c-5b2860387726_CT-02_P7-36_D800_29-03-2026.xlsx
+++ b/SGC-CKN/Excel/bf6734bd-047d-4687-8d8c-5b2860387726_CT-02_P7-36_D800_29-03-2026.xlsx
@@ -1259,7 +1259,7 @@
         <v>29</v>
       </c>
       <c r="F11" s="5">
-        <v>-0.71</v>
+        <v>0</v>
       </c>
       <c r="G11" s="5">
         <v>-7.19</v>
@@ -1268,10 +1268,10 @@
         <v>0.33</v>
       </c>
       <c r="I11" s="5">
-        <v>6.48</v>
+        <v>7.19</v>
       </c>
       <c r="J11" s="8">
-        <v>19.44</v>
+        <v>21.57</v>
       </c>
       <c r="K11" s="6" t="s">
         <v>30</v>
@@ -1542,16 +1542,16 @@
         <v>-40.1</v>
       </c>
       <c r="G19" s="32">
-        <v>-43.1</v>
+        <v>-43.4</v>
       </c>
       <c r="H19" s="32">
         <v>0.82</v>
       </c>
       <c r="I19" s="32">
-        <v>3</v>
+        <v>3.3</v>
       </c>
       <c r="J19" s="25">
-        <v>3.67</v>
+        <v>4.04</v>
       </c>
       <c r="K19" s="33" t="s">
         <v>35</v>
@@ -1574,19 +1574,19 @@
         <v>68</v>
       </c>
       <c r="F20" s="35">
-        <v>-43.1</v>
+        <v>-43.4</v>
       </c>
       <c r="G20" s="35">
-        <v>-44.78</v>
+        <v>-44.77</v>
       </c>
       <c r="H20" s="35">
         <v>0.82</v>
       </c>
       <c r="I20" s="35">
+        <v>1.37</v>
+      </c>
+      <c r="J20" s="25">
         <v>1.68</v>
-      </c>
-      <c r="J20" s="25">
-        <v>2.06</v>
       </c>
       <c r="K20" s="36" t="s">
         <v>35</v>
@@ -1741,7 +1741,7 @@
         <v>1</v>
       </c>
       <c r="E2" s="5">
-        <v>-0.71</v>
+        <v>0</v>
       </c>
       <c r="F2" s="5">
         <v>-7.19</v>
@@ -1750,10 +1750,10 @@
         <v>0.33</v>
       </c>
       <c r="H2" s="5">
-        <v>6.48</v>
+        <v>7.19</v>
       </c>
       <c r="I2" s="8">
-        <v>19.44</v>
+        <v>21.57</v>
       </c>
     </row>
     <row r="3" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1976,16 +1976,16 @@
         <v>-40.1</v>
       </c>
       <c r="F10" s="32">
-        <v>-43.1</v>
+        <v>-43.4</v>
       </c>
       <c r="G10" s="32">
         <v>0.82</v>
       </c>
       <c r="H10" s="32">
-        <v>3</v>
+        <v>3.3</v>
       </c>
       <c r="I10" s="25">
-        <v>3.67</v>
+        <v>4.04</v>
       </c>
     </row>
     <row r="11" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -2002,19 +2002,19 @@
         <v>1</v>
       </c>
       <c r="E11" s="35">
-        <v>-43.1</v>
+        <v>-43.4</v>
       </c>
       <c r="F11" s="35">
-        <v>-44.78</v>
+        <v>-44.77</v>
       </c>
       <c r="G11" s="35">
         <v>0.82</v>
       </c>
       <c r="H11" s="35">
+        <v>1.37</v>
+      </c>
+      <c r="I11" s="25">
         <v>1.68</v>
-      </c>
-      <c r="I11" s="25">
-        <v>2.06</v>
       </c>
     </row>
     <row r="12" ht="28" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -2031,19 +2031,19 @@
         <v>10</v>
       </c>
       <c r="E12" s="40">
-        <v>-0.71</v>
+        <v>0</v>
       </c>
       <c r="F12" s="40">
-        <v>-44.78</v>
+        <v>-44.77</v>
       </c>
       <c r="G12" s="40">
         <v>18.35</v>
       </c>
       <c r="H12" s="40">
-        <v>44.07</v>
+        <v>44.77</v>
       </c>
       <c r="I12" s="40">
-        <v>2.4</v>
+        <v>2.44</v>
       </c>
     </row>
   </sheetData>
